--- a/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$130</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4569" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4707" uniqueCount="630">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T10:02:39+00:00</t>
+    <t>2024-03-19T08:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -647,13 +647,10 @@
 </t>
   </si>
   <si>
-    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
+    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie (Synonyme : secteurConventionnement).</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire le secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
-  </si>
-  <si>
-    <t>Synonyme : secteurConventionnement</t>
   </si>
   <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-hascas</t>
@@ -1416,6 +1413,69 @@
     <t>Optional Extension Element - found in all resources.</t>
   </si>
   <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.telecom.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
+  &lt;code value="MSSANTE"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/ValueSet/fr-email-type</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
     <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
   </si>
   <si>
@@ -1435,13 +1495,7 @@
     <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.id</t>
   </si>
   <si>
-    <t>PractitionerRole.telecom.extension.id</t>
-  </si>
-  <si>
     <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.extension</t>
   </si>
   <si>
     <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type</t>
@@ -1457,9 +1511,6 @@
 PER pour une BAL personnelle, rattachée à une personne physique</t>
   </si>
   <si>
-    <t>An Extension</t>
-  </si>
-  <si>
     <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.id</t>
   </si>
   <si>
@@ -1472,43 +1523,19 @@
     <t>PractitionerRole.telecom.extension.extension.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
     <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.url</t>
   </si>
   <si>
     <t>PractitionerRole.telecom.extension.extension.url</t>
   </si>
   <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
     <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type.value[x]</t>
   </si>
   <si>
     <t>PractitionerRole.telecom.extension.extension.value[x]</t>
   </si>
   <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
   </si>
   <si>
     <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:description</t>
@@ -1636,16 +1663,10 @@
     <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.url</t>
   </si>
   <si>
-    <t>PractitionerRole.telecom.extension.url</t>
-  </si>
-  <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata</t>
   </si>
   <si>
     <t>PractitionerRole.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.telecom.extension.value[x]</t>
   </si>
   <si>
     <t>base64Binary
@@ -2269,7 +2290,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN126"/>
+  <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="100.33203125" customWidth="true" bestFit="true"/>
@@ -4405,9 +4426,7 @@
       <c r="M19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N19" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4485,13 +4504,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
@@ -4513,13 +4532,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4599,13 +4618,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4627,13 +4646,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4713,10 +4732,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4742,16 +4761,16 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4800,7 +4819,7 @@
         <v>117</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4829,10 +4848,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4855,17 +4874,17 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4902,10 +4921,10 @@
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AC23" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
@@ -4914,7 +4933,7 @@
         <v>117</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4929,27 +4948,27 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -4971,17 +4990,17 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -5030,7 +5049,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5045,24 +5064,24 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5171,10 +5190,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5285,10 +5304,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5314,16 +5333,16 @@
         <v>173</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -5348,31 +5367,31 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="Z27" t="s" s="2">
+      <c r="AA27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5390,7 +5409,7 @@
         <v>102</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5401,10 +5420,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5427,19 +5446,19 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5467,28 +5486,28 @@
         <v>153</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5503,10 +5522,10 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5517,10 +5536,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5546,16 +5565,16 @@
         <v>137</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5565,46 +5584,46 @@
         <v>77</v>
       </c>
       <c r="S29" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="T29" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="T29" t="s" s="2">
+      <c r="U29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5619,13 +5638,13 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5633,10 +5652,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5662,13 +5681,13 @@
         <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5682,43 +5701,43 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5733,13 +5752,13 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5747,10 +5766,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5773,16 +5792,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5832,7 +5851,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5844,16 +5863,16 @@
         <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AK31" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AL31" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5861,10 +5880,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5887,16 +5906,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5946,7 +5965,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5958,16 +5977,16 @@
         <v>100</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AK32" t="s" s="2">
+      <c r="AL32" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5975,13 +5994,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>77</v>
@@ -6003,17 +6022,17 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -6062,7 +6081,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6077,24 +6096,24 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6203,10 +6222,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6317,10 +6336,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6346,16 +6365,16 @@
         <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6380,31 +6399,31 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Y36" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="Y36" t="s" s="2">
+      <c r="Z36" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="Z36" t="s" s="2">
+      <c r="AA36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6422,7 +6441,7 @@
         <v>102</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6433,10 +6452,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6459,19 +6478,19 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6499,28 +6518,28 @@
         <v>153</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="Z37" t="s" s="2">
+      <c r="AA37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6535,10 +6554,10 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6549,10 +6568,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6578,16 +6597,16 @@
         <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6597,46 +6616,46 @@
         <v>77</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="T38" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6651,13 +6670,13 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6665,10 +6684,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6694,13 +6713,13 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6714,43 +6733,43 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6765,13 +6784,13 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6779,10 +6798,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6805,16 +6824,16 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6864,7 +6883,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6876,16 +6895,16 @@
         <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AK40" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AK40" t="s" s="2">
+      <c r="AL40" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6893,10 +6912,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6919,16 +6938,16 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6978,7 +6997,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6990,16 +7009,16 @@
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AK41" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AK41" t="s" s="2">
+      <c r="AL41" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -7007,10 +7026,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7033,26 +7052,26 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="O42" t="s" s="2">
+      <c r="P42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q42" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="P42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q42" t="s" s="2">
-        <v>322</v>
-      </c>
       <c r="R42" t="s" s="2">
         <v>77</v>
       </c>
@@ -7096,7 +7115,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7111,24 +7130,24 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>325</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7151,19 +7170,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -7212,7 +7231,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7224,27 +7243,27 @@
         <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7353,10 +7372,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7467,10 +7486,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7493,16 +7512,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7552,25 +7571,25 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI46" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7581,10 +7600,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7607,69 +7626,69 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="R47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="R47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>350</v>
-      </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7677,16 +7696,16 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7697,10 +7716,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7723,16 +7742,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7782,7 +7801,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7794,13 +7813,13 @@
         <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7811,10 +7830,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7837,16 +7856,16 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>362</v>
-      </c>
       <c r="N49" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7896,7 +7915,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7908,13 +7927,13 @@
         <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7925,10 +7944,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7951,19 +7970,19 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7991,16 +8010,16 @@
         <v>163</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Z50" t="s" s="2">
+      <c r="AA50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB50" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8010,7 +8029,7 @@
         <v>117</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8025,13 +8044,13 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM50" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -8039,13 +8058,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>77</v>
@@ -8067,19 +8086,19 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="M51" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -8104,11 +8123,11 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -8126,7 +8145,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8141,13 +8160,13 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM51" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -8155,13 +8174,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>77</v>
@@ -8183,19 +8202,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="M52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8220,11 +8239,11 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -8242,7 +8261,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8257,13 +8276,13 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM52" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -8271,13 +8290,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>77</v>
@@ -8299,19 +8318,19 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8336,11 +8355,11 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -8358,7 +8377,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8373,13 +8392,13 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM53" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -8387,13 +8406,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C54" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>77</v>
@@ -8415,19 +8434,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M54" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8452,11 +8471,11 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8474,7 +8493,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8489,13 +8508,13 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM54" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8503,13 +8522,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>77</v>
@@ -8531,19 +8550,19 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M55" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8568,11 +8587,11 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8590,7 +8609,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8605,13 +8624,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM55" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8619,13 +8638,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>77</v>
@@ -8647,19 +8666,19 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M56" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8684,11 +8703,11 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8706,7 +8725,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8721,13 +8740,13 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM56" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8735,13 +8754,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C57" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
@@ -8763,19 +8782,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M57" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8800,11 +8819,11 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8822,7 +8841,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8837,13 +8856,13 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM57" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8851,10 +8870,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8877,16 +8896,16 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8915,11 +8934,11 @@
         <v>177</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8936,7 +8955,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8951,13 +8970,13 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8965,10 +8984,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8991,16 +9010,16 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="N59" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9050,7 +9069,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9062,27 +9081,27 @@
         <v>100</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>417</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9105,16 +9124,16 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>421</v>
-      </c>
       <c r="N60" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9164,7 +9183,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9176,13 +9195,13 @@
         <v>100</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -9193,10 +9212,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9219,17 +9238,17 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -9266,17 +9285,17 @@
         <v>77</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC61" s="2"/>
       <c r="AD61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9288,16 +9307,16 @@
         <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AK61" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AK61" t="s" s="2">
+      <c r="AL61" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -9305,13 +9324,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>77</v>
@@ -9333,17 +9352,17 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9392,7 +9411,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9404,16 +9423,16 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AK62" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AK62" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="AL62" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -9421,10 +9440,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9533,10 +9552,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9647,16 +9666,16 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C65" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="B65" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>446</v>
-      </c>
       <c r="D65" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9675,17 +9694,15 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>114</v>
-      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9763,14 +9780,12 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="B66" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>451</v>
-      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9782,7 +9797,7 @@
         <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>77</v>
@@ -9791,13 +9806,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>452</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>453</v>
+        <v>105</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>454</v>
+        <v>106</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9848,25 +9863,25 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9877,10 +9892,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9891,7 +9906,7 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9903,13 +9918,13 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>105</v>
+        <v>453</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>106</v>
+        <v>454</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9948,37 +9963,37 @@
         <v>77</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9989,21 +10004,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
@@ -10015,16 +10030,16 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>112</v>
+        <v>457</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>113</v>
+        <v>458</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>114</v>
+        <v>459</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10032,7 +10047,7 @@
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>77</v>
+        <v>460</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>77</v>
@@ -10062,31 +10077,31 @@
         <v>77</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>118</v>
+        <v>461</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
@@ -10103,14 +10118,12 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>460</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>77</v>
       </c>
@@ -10131,13 +10144,13 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10149,7 +10162,7 @@
         <v>77</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>77</v>
+        <v>466</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>77</v>
@@ -10164,13 +10177,11 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>77</v>
+        <v>467</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -10188,25 +10199,25 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>118</v>
+        <v>468</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -10217,12 +10228,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="D70" t="s" s="2">
         <v>77</v>
       </c>
@@ -10243,13 +10256,13 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>104</v>
+        <v>471</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>105</v>
+        <v>472</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>106</v>
+        <v>473</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10300,25 +10313,25 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -10329,10 +10342,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10343,7 +10356,7 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
@@ -10355,13 +10368,13 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>467</v>
+        <v>105</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>462</v>
+        <v>106</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10400,37 +10413,37 @@
         <v>77</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -10441,21 +10454,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>77</v>
@@ -10467,16 +10480,16 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>470</v>
+        <v>112</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>471</v>
+        <v>113</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>472</v>
+        <v>114</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10484,7 +10497,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>77</v>
@@ -10514,31 +10527,31 @@
         <v>77</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>473</v>
+        <v>118</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
@@ -10555,12 +10568,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="D73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10581,13 +10596,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>251</v>
+        <v>111</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10614,11 +10629,13 @@
         <v>77</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>478</v>
+        <v>77</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
@@ -10636,25 +10653,25 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>479</v>
+        <v>118</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -10665,14 +10682,12 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="B74" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C74" t="s" s="2">
-        <v>481</v>
-      </c>
+      <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>77</v>
       </c>
@@ -10693,13 +10708,13 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>482</v>
+        <v>105</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>462</v>
+        <v>106</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10750,25 +10765,25 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10779,10 +10794,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10793,7 +10808,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
@@ -10805,13 +10820,13 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>105</v>
+        <v>453</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>106</v>
+        <v>454</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10850,37 +10865,37 @@
         <v>77</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -10891,10 +10906,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10902,10 +10917,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>77</v>
@@ -10917,22 +10932,24 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>77</v>
+        <v>477</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>77</v>
@@ -10962,37 +10979,37 @@
         <v>77</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>118</v>
+        <v>461</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -11006,7 +11023,7 @@
         <v>485</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11014,7 +11031,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>88</v>
@@ -11029,24 +11046,22 @@
         <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>137</v>
+        <v>250</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>77</v>
@@ -11064,13 +11079,11 @@
         <v>77</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>77</v>
+        <v>487</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>77</v>
@@ -11088,19 +11101,19 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
@@ -11117,12 +11130,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>77</v>
       </c>
@@ -11143,13 +11158,13 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11200,25 +11215,25 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>479</v>
+        <v>118</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -11229,14 +11244,12 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>77</v>
       </c>
@@ -11245,7 +11258,7 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
@@ -11257,13 +11270,13 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>467</v>
+        <v>105</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>462</v>
+        <v>106</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11314,25 +11327,25 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -11343,10 +11356,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11357,7 +11370,7 @@
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>77</v>
@@ -11369,13 +11382,13 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>105</v>
+        <v>453</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>106</v>
+        <v>454</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11414,37 +11427,37 @@
         <v>77</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -11455,10 +11468,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11466,10 +11479,10 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>77</v>
@@ -11481,22 +11494,24 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>77</v>
+        <v>489</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>77</v>
@@ -11526,37 +11541,37 @@
         <v>77</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>118</v>
+        <v>461</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -11567,10 +11582,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11578,7 +11593,7 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>88</v>
@@ -11593,24 +11608,22 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>488</v>
+        <v>77</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>77</v>
@@ -11652,19 +11665,19 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>77</v>
@@ -11681,12 +11694,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C83" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="D83" t="s" s="2">
         <v>77</v>
       </c>
@@ -11695,7 +11710,7 @@
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>77</v>
@@ -11707,13 +11722,13 @@
         <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11764,25 +11779,25 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>479</v>
+        <v>118</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
@@ -11793,14 +11808,12 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>77</v>
       </c>
@@ -11821,13 +11834,13 @@
         <v>77</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>495</v>
+        <v>105</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>462</v>
+        <v>106</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11878,25 +11891,25 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>77</v>
@@ -11907,10 +11920,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11921,7 +11934,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>77</v>
@@ -11933,13 +11946,13 @@
         <v>77</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>105</v>
+        <v>453</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>106</v>
+        <v>454</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11978,37 +11991,37 @@
         <v>77</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
@@ -12019,10 +12032,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12030,10 +12043,10 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>77</v>
@@ -12045,22 +12058,24 @@
         <v>77</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>77</v>
+        <v>496</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>77</v>
@@ -12090,37 +12105,37 @@
         <v>77</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>118</v>
+        <v>461</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
@@ -12131,10 +12146,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12142,7 +12157,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>88</v>
@@ -12157,24 +12172,22 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>494</v>
+        <v>77</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>77</v>
@@ -12216,19 +12229,19 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>77</v>
@@ -12245,12 +12258,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="D88" t="s" s="2">
         <v>77</v>
       </c>
@@ -12271,13 +12286,13 @@
         <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>476</v>
+        <v>503</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12328,25 +12343,25 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>479</v>
+        <v>118</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -12357,14 +12372,12 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>77</v>
       </c>
@@ -12373,7 +12386,7 @@
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>77</v>
@@ -12385,13 +12398,13 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>467</v>
+        <v>105</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>462</v>
+        <v>106</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12442,25 +12455,25 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -12471,10 +12484,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12485,7 +12498,7 @@
         <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>77</v>
@@ -12497,13 +12510,13 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>105</v>
+        <v>453</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>106</v>
+        <v>454</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12542,37 +12555,37 @@
         <v>77</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -12583,10 +12596,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12594,10 +12607,10 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>77</v>
@@ -12609,22 +12622,24 @@
         <v>77</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>77</v>
+        <v>502</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>77</v>
@@ -12654,37 +12669,37 @@
         <v>77</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>118</v>
+        <v>461</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
@@ -12695,10 +12710,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12706,7 +12721,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>88</v>
@@ -12721,24 +12736,22 @@
         <v>77</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>501</v>
+        <v>77</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>77</v>
@@ -12780,19 +12793,19 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>77</v>
@@ -12809,12 +12822,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C93" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>509</v>
+      </c>
       <c r="D93" t="s" s="2">
         <v>77</v>
       </c>
@@ -12823,7 +12838,7 @@
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>77</v>
@@ -12835,13 +12850,13 @@
         <v>77</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12892,25 +12907,25 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>479</v>
+        <v>118</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
@@ -12921,14 +12936,12 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>77</v>
       </c>
@@ -12949,13 +12962,13 @@
         <v>77</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>508</v>
+        <v>105</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>462</v>
+        <v>106</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13006,25 +13019,25 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
@@ -13035,10 +13048,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13049,7 +13062,7 @@
         <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>77</v>
@@ -13061,13 +13074,13 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>105</v>
+        <v>453</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>106</v>
+        <v>454</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13106,37 +13119,37 @@
         <v>77</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
@@ -13147,10 +13160,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13158,10 +13171,10 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>77</v>
@@ -13173,22 +13186,24 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>77</v>
+        <v>509</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>77</v>
@@ -13218,37 +13233,37 @@
         <v>77</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>118</v>
+        <v>461</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -13259,10 +13274,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13270,7 +13285,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>88</v>
@@ -13285,24 +13300,22 @@
         <v>77</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>507</v>
+        <v>77</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>77</v>
@@ -13344,19 +13357,19 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>77</v>
@@ -13373,12 +13386,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C98" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="D98" t="s" s="2">
         <v>77</v>
       </c>
@@ -13399,13 +13414,13 @@
         <v>77</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>317</v>
+        <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>476</v>
+        <v>516</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13456,25 +13471,25 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>479</v>
+        <v>118</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>77</v>
@@ -13485,14 +13500,12 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>514</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>77</v>
       </c>
@@ -13513,13 +13526,13 @@
         <v>77</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>515</v>
+        <v>105</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>462</v>
+        <v>106</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13570,25 +13583,25 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>77</v>
@@ -13599,10 +13612,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13613,7 +13626,7 @@
         <v>78</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>77</v>
@@ -13625,13 +13638,13 @@
         <v>77</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>105</v>
+        <v>453</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>106</v>
+        <v>454</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13670,37 +13683,37 @@
         <v>77</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
@@ -13711,10 +13724,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13722,10 +13735,10 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>77</v>
@@ -13737,22 +13750,24 @@
         <v>77</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>77</v>
+        <v>515</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>77</v>
@@ -13782,37 +13797,37 @@
         <v>77</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>118</v>
+        <v>461</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
@@ -13823,10 +13838,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13834,7 +13849,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>88</v>
@@ -13849,24 +13864,22 @@
         <v>77</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>137</v>
+        <v>316</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>514</v>
+        <v>77</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>77</v>
@@ -13908,19 +13921,19 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>77</v>
@@ -13937,12 +13950,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C103" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="D103" t="s" s="2">
         <v>77</v>
       </c>
@@ -13963,13 +13978,13 @@
         <v>77</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>317</v>
+        <v>111</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>476</v>
+        <v>523</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14020,25 +14035,25 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>479</v>
+        <v>118</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
@@ -14049,10 +14064,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>521</v>
+        <v>480</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14060,7 +14075,7 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>88</v>
@@ -14075,24 +14090,22 @@
         <v>77</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>470</v>
+        <v>105</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>522</v>
+        <v>77</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>77</v>
@@ -14134,10 +14147,10 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>473</v>
+        <v>107</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>88</v>
@@ -14152,7 +14165,7 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
@@ -14163,10 +14176,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>524</v>
+        <v>482</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14189,13 +14202,13 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>525</v>
+        <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14234,37 +14247,37 @@
         <v>77</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>479</v>
+        <v>118</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -14278,7 +14291,7 @@
         <v>526</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>527</v>
+        <v>484</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14298,19 +14311,19 @@
         <v>77</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>528</v>
+        <v>457</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>529</v>
+        <v>458</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>530</v>
+        <v>459</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14318,10 +14331,10 @@
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>77</v>
+        <v>522</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>531</v>
+        <v>77</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>77</v>
@@ -14336,13 +14349,13 @@
         <v>77</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>532</v>
+        <v>77</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>533</v>
+        <v>77</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>77</v>
@@ -14360,28 +14373,28 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>534</v>
+        <v>461</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>535</v>
+        <v>77</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>536</v>
+        <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>537</v>
+        <v>102</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>538</v>
+        <v>77</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>77</v>
@@ -14389,10 +14402,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>540</v>
+        <v>486</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14400,35 +14413,31 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>104</v>
+        <v>316</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>541</v>
+        <v>464</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>544</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>77</v>
       </c>
@@ -14476,7 +14485,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>545</v>
+        <v>468</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14491,13 +14500,13 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>546</v>
+        <v>77</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>547</v>
+        <v>102</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>77</v>
@@ -14505,10 +14514,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>548</v>
+        <v>528</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>549</v>
+        <v>456</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14516,7 +14525,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>88</v>
@@ -14525,32 +14534,30 @@
         <v>77</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>550</v>
+        <v>457</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>551</v>
+        <v>458</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>553</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>77</v>
+        <v>529</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>77</v>
@@ -14568,13 +14575,13 @@
         <v>77</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>554</v>
+        <v>77</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>555</v>
+        <v>77</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>77</v>
@@ -14592,28 +14599,28 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>556</v>
+        <v>461</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>557</v>
+        <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>558</v>
+        <v>102</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>559</v>
+        <v>77</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>77</v>
@@ -14621,10 +14628,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>560</v>
+        <v>530</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>561</v>
+        <v>463</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14635,7 +14642,7 @@
         <v>78</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>77</v>
@@ -14644,20 +14651,18 @@
         <v>77</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>562</v>
+        <v>531</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>563</v>
+        <v>464</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>565</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -14706,7 +14711,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>566</v>
+        <v>468</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14721,10 +14726,10 @@
         <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
@@ -14735,10 +14740,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>567</v>
+        <v>532</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>568</v>
+        <v>533</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14746,7 +14751,7 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>88</v>
@@ -14761,16 +14766,16 @@
         <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>284</v>
+        <v>173</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>569</v>
+        <v>534</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>570</v>
+        <v>535</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>287</v>
+        <v>536</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14781,7 +14786,7 @@
         <v>77</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>77</v>
+        <v>537</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>77</v>
@@ -14796,13 +14801,13 @@
         <v>77</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>77</v>
+        <v>538</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>77</v>
+        <v>539</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>77</v>
@@ -14820,7 +14825,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>571</v>
+        <v>540</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14829,19 +14834,19 @@
         <v>88</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>100</v>
+        <v>541</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>289</v>
+        <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>102</v>
+        <v>542</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>572</v>
+        <v>543</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>292</v>
+        <v>544</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>77</v>
@@ -14849,10 +14854,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>573</v>
+        <v>545</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>573</v>
+        <v>546</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14860,10 +14865,10 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>89</v>
@@ -14872,21 +14877,23 @@
         <v>77</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>574</v>
+        <v>104</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>575</v>
+        <v>547</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>576</v>
+        <v>548</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="O111" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>77</v>
       </c>
@@ -14934,13 +14941,13 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>573</v>
+        <v>551</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>100</v>
@@ -14949,13 +14956,13 @@
         <v>101</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>77</v>
+        <v>552</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>578</v>
+        <v>553</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>77</v>
+        <v>280</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>77</v>
@@ -14963,10 +14970,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>579</v>
+        <v>554</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14983,22 +14990,26 @@
         <v>77</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>105</v>
+        <v>556</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>559</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>77</v>
       </c>
@@ -15022,13 +15033,13 @@
         <v>77</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>77</v>
+        <v>560</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>77</v>
+        <v>561</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>77</v>
@@ -15046,7 +15057,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>107</v>
+        <v>562</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15055,19 +15066,19 @@
         <v>88</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>77</v>
+        <v>563</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>108</v>
+        <v>564</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>77</v>
+        <v>565</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>77</v>
@@ -15075,21 +15086,21 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>77</v>
@@ -15098,19 +15109,19 @@
         <v>77</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>111</v>
+        <v>568</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>112</v>
+        <v>569</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>113</v>
+        <v>570</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>114</v>
+        <v>571</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15148,37 +15159,37 @@
         <v>77</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>118</v>
+        <v>572</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
@@ -15189,46 +15200,44 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>582</v>
+        <v>77</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J114" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>77</v>
       </c>
@@ -15276,28 +15285,28 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>119</v>
+        <v>288</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>102</v>
+        <v>578</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>77</v>
+        <v>291</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>77</v>
@@ -15305,10 +15314,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15319,10 +15328,10 @@
         <v>78</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>77</v>
@@ -15331,16 +15340,16 @@
         <v>77</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>173</v>
+        <v>580</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>530</v>
+        <v>583</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15366,13 +15375,13 @@
         <v>77</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>589</v>
+        <v>77</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>590</v>
+        <v>77</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>77</v>
@@ -15390,7 +15399,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15408,7 +15417,7 @@
         <v>77</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>77</v>
@@ -15419,10 +15428,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15445,13 +15454,13 @@
         <v>77</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>317</v>
+        <v>104</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>592</v>
+        <v>105</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>593</v>
+        <v>106</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15502,7 +15511,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>591</v>
+        <v>107</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15511,16 +15520,16 @@
         <v>88</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>578</v>
+        <v>108</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>77</v>
@@ -15531,21 +15540,21 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>77</v>
@@ -15557,16 +15566,16 @@
         <v>77</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>595</v>
+        <v>111</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>596</v>
+        <v>112</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>597</v>
+        <v>113</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>598</v>
+        <v>114</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15604,37 +15613,37 @@
         <v>77</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>594</v>
+        <v>118</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>578</v>
+        <v>102</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>77</v>
@@ -15645,44 +15654,46 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>77</v>
+        <v>588</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>595</v>
+        <v>111</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="O118" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>77</v>
       </c>
@@ -15730,25 +15741,25 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>578</v>
+        <v>102</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>77</v>
@@ -15759,10 +15770,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15773,10 +15784,10 @@
         <v>78</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>77</v>
@@ -15785,15 +15796,17 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>574</v>
+        <v>173</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -15818,13 +15831,13 @@
         <v>77</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>77</v>
+        <v>595</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>77</v>
+        <v>596</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>77</v>
@@ -15842,7 +15855,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15860,7 +15873,7 @@
         <v>77</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
@@ -15871,10 +15884,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15897,13 +15910,13 @@
         <v>77</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>104</v>
+        <v>316</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>105</v>
+        <v>598</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>106</v>
+        <v>599</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15954,7 +15967,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>107</v>
+        <v>597</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15963,16 +15976,16 @@
         <v>88</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>108</v>
+        <v>584</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>77</v>
@@ -15983,21 +15996,21 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>77</v>
@@ -16009,16 +16022,16 @@
         <v>77</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>111</v>
+        <v>601</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>112</v>
+        <v>602</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>113</v>
+        <v>603</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>114</v>
+        <v>604</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16056,37 +16069,37 @@
         <v>77</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>118</v>
+        <v>600</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>102</v>
+        <v>584</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
@@ -16097,46 +16110,44 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>582</v>
+        <v>77</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>111</v>
+        <v>601</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>77</v>
       </c>
@@ -16184,25 +16195,25 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>102</v>
+        <v>584</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -16224,13 +16235,13 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>77</v>
@@ -16239,7 +16250,7 @@
         <v>77</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>104</v>
+        <v>580</v>
       </c>
       <c r="L123" t="s" s="2">
         <v>609</v>
@@ -16247,9 +16258,7 @@
       <c r="M123" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="N123" t="s" s="2">
-        <v>530</v>
-      </c>
+      <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>77</v>
@@ -16301,10 +16310,10 @@
         <v>608</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>100</v>
@@ -16316,7 +16325,7 @@
         <v>77</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>108</v>
+        <v>584</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>77</v>
@@ -16353,17 +16362,15 @@
         <v>77</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>284</v>
+        <v>104</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>612</v>
+        <v>105</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>77</v>
@@ -16412,7 +16419,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>611</v>
+        <v>107</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16421,16 +16428,16 @@
         <v>88</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>289</v>
+        <v>77</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>614</v>
+        <v>77</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>578</v>
+        <v>108</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>77</v>
@@ -16441,24 +16448,24 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>77</v>
@@ -16467,16 +16474,16 @@
         <v>77</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>616</v>
+        <v>112</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>617</v>
+        <v>113</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>530</v>
+        <v>114</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16514,37 +16521,37 @@
         <v>77</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>615</v>
+        <v>118</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>578</v>
+        <v>102</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>77</v>
@@ -16555,45 +16562,45 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>77</v>
+        <v>588</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I126" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I126" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="J126" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>619</v>
+        <v>111</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>620</v>
+        <v>589</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>621</v>
+        <v>590</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>357</v>
+        <v>114</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>622</v>
+        <v>217</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -16642,7 +16649,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>618</v>
+        <v>591</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16654,23 +16661,481 @@
         <v>100</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>300</v>
+        <v>119</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL126" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="AM126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN126" t="s" s="2">
+      <c r="N129" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="P130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN130" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN126">
+  <autoFilter ref="A1:AN130">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16680,7 +17145,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI125">
+  <conditionalFormatting sqref="A2:AI129">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4707" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4705" uniqueCount="631">
   <si>
     <t>Property</t>
   </si>
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:36:19+00:00</t>
+    <t>2024-04-03T13:59:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>
@@ -1333,7 +1333,7 @@
     <t>PractitionerRole.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {http://interopsante.org/fhir/StructureDefinition/FrContactPoint}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
 </t>
   </si>
   <si>
@@ -1382,6 +1382,10 @@
     <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
   </si>
   <si>
+    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
     <t>TEL</t>
   </si>
   <si>
@@ -1403,14 +1407,14 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type}
 </t>
   </si>
   <si>
     <t>Type of email | type de messagerie électronique</t>
   </si>
   <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>Extension on the ContactPoint datatype. This extension allows to specify the type of mail used to contact the person (MSSsanté|Apicrypt|OSM|Autre).</t>
   </si>
   <si>
     <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.id</t>
@@ -1446,7 +1450,7 @@
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
-    <t>http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -1470,7 +1474,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>http://interopsante.org/fhir/ValueSet/fr-email-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1685,23 +1689,20 @@
     <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>email</t>
   </si>
   <si>
     <t>Telecommunications form for contact point.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contact-point-system</t>
+    <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.0.1</t>
   </si>
   <si>
     <t>ContactPoint.system</t>
   </si>
   <si>
-    <t>ele-1
-cpt-2</t>
+    <t xml:space="preserve">cpt-2
+</t>
   </si>
   <si>
     <t>XTN.3</t>
@@ -1761,7 +1762,7 @@
     <t>Use of contact point.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contact-point-use</t>
+    <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.0.1</t>
   </si>
   <si>
     <t>ContactPoint.use</t>
@@ -1865,6 +1866,9 @@
   </si>
   <si>
     <t>Indicates which days of the week are available between the start and end Times.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>The days of the week.</t>
@@ -9423,13 +9427,13 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>431</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>433</v>
@@ -9440,10 +9444,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9552,10 +9556,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9646,7 +9650,7 @@
         <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>119</v>
@@ -9655,7 +9659,7 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -9666,13 +9670,13 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="B65" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="C65" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>77</v>
@@ -9694,13 +9698,13 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9760,7 +9764,7 @@
         <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>119</v>
@@ -9769,7 +9773,7 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9780,10 +9784,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9892,10 +9896,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9921,10 +9925,10 @@
         <v>111</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9984,7 +9988,7 @@
         <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>119</v>
@@ -10004,10 +10008,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10033,13 +10037,13 @@
         <v>137</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10047,7 +10051,7 @@
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>77</v>
@@ -10089,7 +10093,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>88</v>
@@ -10118,10 +10122,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10147,10 +10151,10 @@
         <v>149</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10162,7 +10166,7 @@
         <v>77</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>77</v>
@@ -10181,7 +10185,7 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -10199,7 +10203,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10208,7 +10212,7 @@
         <v>88</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>101</v>
@@ -10228,13 +10232,13 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>77</v>
@@ -10256,13 +10260,13 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10322,7 +10326,7 @@
         <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>119</v>
@@ -10342,10 +10346,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10454,10 +10458,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10568,13 +10572,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>77</v>
@@ -10599,10 +10603,10 @@
         <v>111</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10682,10 +10686,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10794,10 +10798,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10823,10 +10827,10 @@
         <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10906,10 +10910,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10935,13 +10939,13 @@
         <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10949,7 +10953,7 @@
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>77</v>
@@ -10991,7 +10995,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>88</v>
@@ -11020,10 +11024,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11049,10 +11053,10 @@
         <v>250</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11083,7 +11087,7 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>77</v>
@@ -11101,7 +11105,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11130,13 +11134,13 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>77</v>
@@ -11161,10 +11165,10 @@
         <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11244,10 +11248,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11356,10 +11360,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11385,10 +11389,10 @@
         <v>111</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11468,10 +11472,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11497,13 +11501,13 @@
         <v>137</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11511,7 +11515,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>77</v>
@@ -11553,7 +11557,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>88</v>
@@ -11582,10 +11586,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11611,10 +11615,10 @@
         <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11665,7 +11669,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11694,13 +11698,13 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>77</v>
@@ -11725,10 +11729,10 @@
         <v>111</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11808,10 +11812,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11920,10 +11924,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11949,10 +11953,10 @@
         <v>111</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12032,10 +12036,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12061,13 +12065,13 @@
         <v>137</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12075,7 +12079,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>77</v>
@@ -12117,7 +12121,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>88</v>
@@ -12146,10 +12150,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12175,10 +12179,10 @@
         <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12229,7 +12233,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12258,13 +12262,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>77</v>
@@ -12289,10 +12293,10 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12372,10 +12376,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12484,10 +12488,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12513,10 +12517,10 @@
         <v>111</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12596,10 +12600,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12625,13 +12629,13 @@
         <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12639,7 +12643,7 @@
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>77</v>
@@ -12681,7 +12685,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>88</v>
@@ -12710,10 +12714,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12739,10 +12743,10 @@
         <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12793,7 +12797,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12822,13 +12826,13 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>77</v>
@@ -12853,10 +12857,10 @@
         <v>111</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12936,10 +12940,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13048,10 +13052,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13077,10 +13081,10 @@
         <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13160,10 +13164,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13189,13 +13193,13 @@
         <v>137</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13203,7 +13207,7 @@
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>77</v>
@@ -13245,7 +13249,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>88</v>
@@ -13274,10 +13278,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13303,10 +13307,10 @@
         <v>104</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13357,7 +13361,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13386,13 +13390,13 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>77</v>
@@ -13417,10 +13421,10 @@
         <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13500,10 +13504,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13612,10 +13616,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13641,10 +13645,10 @@
         <v>111</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13724,10 +13728,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13753,13 +13757,13 @@
         <v>137</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13767,7 +13771,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>77</v>
@@ -13809,7 +13813,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>88</v>
@@ -13838,10 +13842,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13867,10 +13871,10 @@
         <v>316</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13921,7 +13925,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13950,13 +13954,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>77</v>
@@ -13981,10 +13985,10 @@
         <v>111</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14064,10 +14068,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14176,10 +14180,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14205,10 +14209,10 @@
         <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14288,10 +14292,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14317,13 +14321,13 @@
         <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14331,7 +14335,7 @@
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>77</v>
@@ -14373,7 +14377,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>88</v>
@@ -14402,10 +14406,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14431,10 +14435,10 @@
         <v>316</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14485,7 +14489,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14514,10 +14518,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14543,13 +14547,13 @@
         <v>137</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14557,7 +14561,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>77</v>
@@ -14599,7 +14603,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>88</v>
@@ -14628,10 +14632,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14654,13 +14658,13 @@
         <v>77</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14711,7 +14715,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14740,10 +14744,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14769,14 +14773,12 @@
         <v>173</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N110" t="s" s="2">
         <v>536</v>
       </c>
+      <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>77</v>
@@ -14950,7 +14952,7 @@
         <v>88</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>101</v>
@@ -15066,7 +15068,7 @@
         <v>88</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>101</v>
@@ -15180,7 +15182,7 @@
         <v>88</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>101</v>
@@ -15234,9 +15236,7 @@
       <c r="M114" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="N114" t="s" s="2">
-        <v>286</v>
-      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>77</v>
@@ -15294,10 +15294,10 @@
         <v>88</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>288</v>
+        <v>101</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>102</v>
@@ -15805,7 +15805,7 @@
         <v>594</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>536</v>
+        <v>595</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15834,10 +15834,10 @@
         <v>243</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>77</v>
@@ -15884,10 +15884,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15913,10 +15913,10 @@
         <v>316</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15967,7 +15967,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15996,10 +15996,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16022,16 +16022,16 @@
         <v>77</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16081,7 +16081,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16110,10 +16110,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16136,16 +16136,16 @@
         <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16195,7 +16195,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16224,10 +16224,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16253,10 +16253,10 @@
         <v>580</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16307,7 +16307,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16336,10 +16336,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16448,10 +16448,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16562,10 +16562,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16678,10 +16678,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16707,13 +16707,13 @@
         <v>104</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>536</v>
+        <v>595</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -16763,7 +16763,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>88</v>
@@ -16792,10 +16792,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16821,10 +16821,10 @@
         <v>283</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>286</v>
@@ -16877,7 +16877,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -16892,7 +16892,7 @@
         <v>288</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>584</v>
@@ -16906,10 +16906,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16935,13 +16935,13 @@
         <v>104</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>536</v>
+        <v>595</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -16991,7 +16991,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17020,10 +17020,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17046,19 +17046,19 @@
         <v>77</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>356</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>77</v>
@@ -17107,7 +17107,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17125,7 +17125,7 @@
         <v>77</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>77</v>

--- a/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:59:51+00:00</t>
+    <t>2024-04-03T14:08:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:18:25+00:00</t>
+    <t>2024-04-03T14:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:35:17+00:00</t>
+    <t>2024-04-03T14:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-3</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:54:13+00:00</t>
+    <t>2024-04-08T13:06:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr, monserviceclient.annuaire@esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:06:58+00:00</t>
+    <t>2024-04-08T13:14:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T14:07:36+00:00</t>
+    <t>2024-04-08T14:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
